--- a/survey_templates/035_resource_development_assessment--survey_templates.xlsx
+++ b/survey_templates/035_resource_development_assessment--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1106,8 +1106,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Not Applicable'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat_applicable'}</t>
+          <t>somewhat_applicable</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat Applicable'}</t>
+          <t>Somewhat Applicable</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'very_applicable'}</t>
+          <t>very_applicable</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Very Applicable'}</t>
+          <t>Very Applicable</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'extremely_applicable'}</t>
+          <t>extremely_applicable</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Extremely Applicable'}</t>
+          <t>Extremely Applicable</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
